--- a/storage/outputs/clasificacion_mantenimiento_perfecto.xlsx
+++ b/storage/outputs/clasificacion_mantenimiento_perfecto.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
